--- a/demo/spec_versions/cargo_shipments.v1.1.0.xlsx
+++ b/demo/spec_versions/cargo_shipments.v1.1.0.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Contract" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Columns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Quality" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Team" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Roles" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>tc_demo</t>
+          <t>dlt_test</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>/Volumes/tc_demo/cargo_landing/raw/shipments</t>
+          <t>/Volumes/dlt_test/cargo_landing/raw/shipments</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
